--- a/docs/evidencia_p0/golden/Observaciones_ESPERA.xlsx
+++ b/docs/evidencia_p0/golden/Observaciones_ESPERA.xlsx
@@ -606,17 +606,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>["ESPERA.E05_PROYECTO_Y_CORREO"]</t>
+          <t>["ESPERA.E05_PROYECTO_Y_CORREO", "HISTORIA.E05_DIAS"]</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
+          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>["ESPERA.E05_SOLO_CORREO"]</t>
+          <t>["ESPERA.E05_SOLO_CORREO", "HISTORIA.E05_DIAS"]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
+          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
         </is>
       </c>
     </row>
@@ -766,17 +766,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>["ESPERA.E05_PROYECTO_Y_CORREO"]</t>
+          <t>["ESPERA.E05_PROYECTO_Y_CORREO", "HISTORIA.E05_DIAS"]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 60 días de espera.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 60 días de espera.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
+          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 60 días de espera.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>["ESPERA.E05_PROYECTO_Y_CORREO"]</t>
+          <t>["ESPERA.E05_PROYECTO_Y_CORREO", "HISTORIA.E05_DIAS"]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1013,12 +1013,12 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>["ESPERA.E05_SOLO_CORREO"]</t>
+          <t>["ESPERA.E05_SOLO_CORREO", "HISTORIA.E05_DIAS"]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1044,12 +1044,12 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 60 días de espera.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>["ESPERA.E05_PROYECTO_Y_CORREO"]</t>
+          <t>["ESPERA.E05_PROYECTO_Y_CORREO", "HISTORIA.E05_DIAS"]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">

--- a/docs/evidencia_p0/golden/Observaciones_ESPERA.xlsx
+++ b/docs/evidencia_p0/golden/Observaciones_ESPERA.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
+          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
         </is>
       </c>
     </row>
@@ -691,12 +691,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
+          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
+          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
+          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona DCE: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite correo al programa consultando fecha estimada de ingreso.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 60 días de espera.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 60 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 60 días de espera.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 60 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 60 días de espera.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
+          <t>{"decisions": {"mail": {}, "resolution": "auto", "structured": true}, "excluded": false, "overrides": {}, "proposal": "Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 60 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.", "resolution_cell": "", "version": 1, "word_overrides": {}}</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1013,7 +1013,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Se remite correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 30 días de espera.</t>
+          <t>Persona DCE: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1044,7 +1044,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso. Al 8 de octubre de 2026, RUS registra 60 días de espera.</t>
+          <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 60 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">

--- a/docs/evidencia_p0/golden/Observaciones_ESPERA.xlsx
+++ b/docs/evidencia_p0/golden/Observaciones_ESPERA.xlsx
@@ -619,6 +619,11 @@
           <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 30 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>PC_IE</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>PROPUESTA</t>
@@ -777,6 +782,11 @@
       <c r="P4" t="inlineStr">
         <is>
           <t>Persona AFT: Medida revisada, a la espera de ingreso efectivo. Al 8 de octubre de 2026, RUS registra 60 días de espera. Se remite proyecto de resolución pidiendo cuenta del ingreso efectivo y correo al programa consultando fecha estimada de ingreso.</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>PC_IE</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
